--- a/Sale_Order_Size (2).xlsx
+++ b/Sale_Order_Size (2).xlsx
@@ -148,31 +148,31 @@
     <t>46#</t>
   </si>
   <si>
-    <t>15E09A7001</t>
-  </si>
-  <si>
-    <t>15F09A7001</t>
-  </si>
-  <si>
-    <t>15G09A7001</t>
-  </si>
-  <si>
-    <t>15H09A7001</t>
-  </si>
-  <si>
-    <t>15I09A7001</t>
-  </si>
-  <si>
-    <t>15J09A7001</t>
-  </si>
-  <si>
-    <t>15K09A7001</t>
-  </si>
-  <si>
-    <t>15L09A7001</t>
-  </si>
-  <si>
-    <t>15M09A7001</t>
+    <t>15E09A8009</t>
+  </si>
+  <si>
+    <t>15F09A8009</t>
+  </si>
+  <si>
+    <t>15G09A8009</t>
+  </si>
+  <si>
+    <t>15H09A8009</t>
+  </si>
+  <si>
+    <t>15I09A8009</t>
+  </si>
+  <si>
+    <t>15J09A8009</t>
+  </si>
+  <si>
+    <t>15K09A8009</t>
+  </si>
+  <si>
+    <t>15L09A8009</t>
+  </si>
+  <si>
+    <t>15M09A8009</t>
   </si>
 </sst>
 </file>

--- a/Sale_Order_Size (2).xlsx
+++ b/Sale_Order_Size (2).xlsx
@@ -148,38 +148,38 @@
     <t>46#</t>
   </si>
   <si>
-    <t>15E09A8009</t>
-  </si>
-  <si>
-    <t>15F09A8009</t>
-  </si>
-  <si>
-    <t>15G09A8009</t>
-  </si>
-  <si>
-    <t>15H09A8009</t>
-  </si>
-  <si>
-    <t>15I09A8009</t>
-  </si>
-  <si>
-    <t>15J09A8009</t>
-  </si>
-  <si>
-    <t>15K09A8009</t>
-  </si>
-  <si>
-    <t>15L09A8009</t>
-  </si>
-  <si>
-    <t>15M09A8009</t>
+    <t>15E09A9042</t>
+  </si>
+  <si>
+    <t>15F09A9042</t>
+  </si>
+  <si>
+    <t>15G09A9042</t>
+  </si>
+  <si>
+    <t>15H09A9042</t>
+  </si>
+  <si>
+    <t>15I09A9042</t>
+  </si>
+  <si>
+    <t>15J09A9042</t>
+  </si>
+  <si>
+    <t>15K09A9042</t>
+  </si>
+  <si>
+    <t>15L09A9042</t>
+  </si>
+  <si>
+    <t>15M09A9042</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -199,13 +199,6 @@
       <b/>
       <color theme="1"/>
       <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <charset val="134"/>
-      <color theme="1"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -289,19 +282,19 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -580,7 +573,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AP36"/>
-  <sheetFormatPr defaultRowHeight="25.15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9.140625" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="25.15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
     <col min="2" max="42" width="6.28515625" customWidth="1"/>

--- a/Sale_Order_Size (2).xlsx
+++ b/Sale_Order_Size (2).xlsx
@@ -148,31 +148,31 @@
     <t>46#</t>
   </si>
   <si>
-    <t>15E09A9042</t>
-  </si>
-  <si>
-    <t>15F09A9042</t>
-  </si>
-  <si>
-    <t>15G09A9042</t>
-  </si>
-  <si>
-    <t>15H09A9042</t>
-  </si>
-  <si>
-    <t>15I09A9042</t>
-  </si>
-  <si>
-    <t>15J09A9042</t>
-  </si>
-  <si>
-    <t>15K09A9042</t>
-  </si>
-  <si>
-    <t>15L09A9042</t>
-  </si>
-  <si>
-    <t>15M09A9042</t>
+    <t>15E09A9125</t>
+  </si>
+  <si>
+    <t>15F09A9125</t>
+  </si>
+  <si>
+    <t>15G09A9125</t>
+  </si>
+  <si>
+    <t>15H09A9125</t>
+  </si>
+  <si>
+    <t>15I09A9125</t>
+  </si>
+  <si>
+    <t>15J09A9125</t>
+  </si>
+  <si>
+    <t>15K09A9125</t>
+  </si>
+  <si>
+    <t>15L09A9125</t>
+  </si>
+  <si>
+    <t>15M09A9125</t>
   </si>
 </sst>
 </file>
@@ -757,13 +757,13 @@
         <v>43</v>
       </c>
       <c r="B3" s="6">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="C3" s="6">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="D3" s="6">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>

--- a/Sale_Order_Size (2).xlsx
+++ b/Sale_Order_Size (2).xlsx
@@ -148,31 +148,31 @@
     <t>46#</t>
   </si>
   <si>
-    <t>15E09A9125</t>
-  </si>
-  <si>
-    <t>15F09A9125</t>
-  </si>
-  <si>
-    <t>15G09A9125</t>
-  </si>
-  <si>
-    <t>15H09A9125</t>
-  </si>
-  <si>
-    <t>15I09A9125</t>
-  </si>
-  <si>
-    <t>15J09A9125</t>
-  </si>
-  <si>
-    <t>15K09A9125</t>
-  </si>
-  <si>
-    <t>15L09A9125</t>
-  </si>
-  <si>
-    <t>15M09A9125</t>
+    <t>15E09A9153</t>
+  </si>
+  <si>
+    <t>15F09A9153</t>
+  </si>
+  <si>
+    <t>15G09A9153</t>
+  </si>
+  <si>
+    <t>15H09A9153</t>
+  </si>
+  <si>
+    <t>15I09A9153</t>
+  </si>
+  <si>
+    <t>15J09A9153</t>
+  </si>
+  <si>
+    <t>15K09A9153</t>
+  </si>
+  <si>
+    <t>15L09A9153</t>
+  </si>
+  <si>
+    <t>15M09A9153</t>
   </si>
 </sst>
 </file>

--- a/Sale_Order_Size (2).xlsx
+++ b/Sale_Order_Size (2).xlsx
@@ -148,31 +148,31 @@
     <t>46#</t>
   </si>
   <si>
-    <t>15E09A9153</t>
-  </si>
-  <si>
-    <t>15F09A9153</t>
-  </si>
-  <si>
-    <t>15G09A9153</t>
-  </si>
-  <si>
-    <t>15H09A9153</t>
-  </si>
-  <si>
-    <t>15I09A9153</t>
-  </si>
-  <si>
-    <t>15J09A9153</t>
-  </si>
-  <si>
-    <t>15K09A9153</t>
-  </si>
-  <si>
-    <t>15L09A9153</t>
-  </si>
-  <si>
-    <t>15M09A9153</t>
+    <t>15E09A9176</t>
+  </si>
+  <si>
+    <t>15F09A9176</t>
+  </si>
+  <si>
+    <t>15G09A9176</t>
+  </si>
+  <si>
+    <t>15H09A9176</t>
+  </si>
+  <si>
+    <t>15I09A9176</t>
+  </si>
+  <si>
+    <t>15J09A9176</t>
+  </si>
+  <si>
+    <t>15K09A9176</t>
+  </si>
+  <si>
+    <t>15L09A9176</t>
+  </si>
+  <si>
+    <t>15M09A9176</t>
   </si>
 </sst>
 </file>
